--- a/dashboards/manufacturing-downtime/datasets/Manufacturing_Line_Productivity.xlsx
+++ b/dashboards/manufacturing-downtime/datasets/Manufacturing_Line_Productivity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Marketing and Product\Guided Projects\IN PROGRESS\Excel Explanatory Dashboard\Manufacturing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\power-bi-dashboard-portfolio\dashboards\manufacturing-downtime\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E10A6F-0A44-4650-8CBD-904967C0A1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5054B2FF-C06C-4E2D-AF50-4A4A76C6A162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FF62ED8-A67E-423F-8325-F23DB684777C}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -195,6 +195,42 @@
   </si>
   <si>
     <t>Mac</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
 </sst>
 </file>
@@ -266,7 +302,113 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.89999084444715716"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -277,6 +419,68 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E8322DF3-53B7-4983-BCF0-03252BE0A96A}" name="Table4" displayName="Table4" ref="A1:F39" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F39" xr:uid="{E8322DF3-53B7-4983-BCF0-03252BE0A96A}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{53B24E1C-2015-4FE8-AA7C-8276B9D1C0F2}" name="Date" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{93E030B5-E5C5-47E7-BF34-B18498B8AC5D}" name="Product"/>
+    <tableColumn id="3" xr3:uid="{6F759B4C-5B9B-4B70-8830-616DCACD5FF5}" name="Batch"/>
+    <tableColumn id="4" xr3:uid="{EA79CB04-60E3-4057-B6DC-86D777949570}" name="Operator"/>
+    <tableColumn id="5" xr3:uid="{AEE5AA5C-C4C0-4F91-9917-36910E8492D9}" name="Start Time" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{0B792672-D0E9-4ABA-BC59-5EF5DCC7C303}" name="End Time" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0691E4DD-F3F6-4B69-8FF9-D396A2C1FF0D}" name="Table3" displayName="Table3" ref="A1:D7" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D7" xr:uid="{0691E4DD-F3F6-4B69-8FF9-D396A2C1FF0D}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{B94DA06A-CC1A-49F7-AE1A-74C74F1BAD55}" name="Product"/>
+    <tableColumn id="2" xr3:uid="{92B23F5E-CAA1-40B7-85FD-249F4E5DEA95}" name="Flavor"/>
+    <tableColumn id="3" xr3:uid="{679F65B2-1FB6-46B0-B912-5262F85B78AA}" name="Size"/>
+    <tableColumn id="4" xr3:uid="{9592B7DC-4A0D-40FA-97CE-0E6CE93593EA}" name="Min batch time"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{060ACABD-13D2-4AF1-A1E0-2364AC3ED0A8}" name="Table1" displayName="Table1" ref="A1:C13" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A1:C13" xr:uid="{060ACABD-13D2-4AF1-A1E0-2364AC3ED0A8}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{89BDC1D0-628D-41DB-BB5D-44C611B5B784}" name="Factor"/>
+    <tableColumn id="2" xr3:uid="{C364A69F-1FD5-429F-A35E-F18C09507522}" name="Description"/>
+    <tableColumn id="3" xr3:uid="{C355EC13-7F33-4889-8BD8-31DF8B82D46F}" name="Operator Error"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0E8966E8-2283-4F30-9A90-28C91012A39C}" name="Table2" displayName="Table2" ref="A2:M40" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A2:M40" xr:uid="{0E8966E8-2283-4F30-9A90-28C91012A39C}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{EA98AFA3-1963-4B64-BDE9-FAE41EC42140}" name="Batch"/>
+    <tableColumn id="2" xr3:uid="{28ADE954-F849-4F5C-8C2A-199AB85B4F9B}" name="1"/>
+    <tableColumn id="3" xr3:uid="{8AA0B442-4037-4222-8818-7AF93131C5D8}" name="2"/>
+    <tableColumn id="4" xr3:uid="{0799C12F-DFF3-44C3-BE9B-F14BD1B735F0}" name="3"/>
+    <tableColumn id="5" xr3:uid="{73030DB5-F50E-47AC-810F-4D4F885AF476}" name="4"/>
+    <tableColumn id="6" xr3:uid="{FF20D4A3-5644-4CA3-B77E-88EA612CC49E}" name="5"/>
+    <tableColumn id="7" xr3:uid="{3683A8B1-1058-4E6E-AC52-DBC79FC08961}" name="6"/>
+    <tableColumn id="8" xr3:uid="{C71F0FAD-CCCF-4554-B188-BBE85D53DF95}" name="7"/>
+    <tableColumn id="9" xr3:uid="{FEB7CC07-6BED-4A20-92A3-5CDA25D2F6A0}" name="8"/>
+    <tableColumn id="10" xr3:uid="{2C8AD808-2DE1-4236-9775-93AAEE0CB21B}" name="9"/>
+    <tableColumn id="11" xr3:uid="{9A3F64F4-6EAD-4ABC-8863-C9A58EFEA9FE}" name="10"/>
+    <tableColumn id="12" xr3:uid="{77CCDA59-DD46-49E0-B857-213068418280}" name="11"/>
+    <tableColumn id="13" xr3:uid="{79D20745-A2D9-415C-9996-B5F57D79B3D5}" name="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,11 +804,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="8.85546875" customWidth="1"/>
     <col min="13" max="13" width="8.85546875" customWidth="1"/>
@@ -1392,6 +1596,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1400,8 +1607,9 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,6 +1713,9 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1515,7 +1726,7 @@
   <cols>
     <col min="1" max="1" width="8.85546875" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1663,6 +1874,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1695,41 +1909,41 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2">
-        <v>7</v>
-      </c>
-      <c r="I2" s="2">
-        <v>8</v>
-      </c>
-      <c r="J2" s="2">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2">
-        <v>10</v>
-      </c>
-      <c r="L2" s="2">
-        <v>11</v>
-      </c>
-      <c r="M2" s="2">
-        <v>12</v>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -2110,5 +2324,8 @@
     <mergeCell ref="B1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>